--- a/data/trans_camb/P5_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 18,7</t>
+          <t>-4,16; 18,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 12,85</t>
+          <t>-8,68; 12,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 4,73</t>
+          <t>-18,18; 4,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 16,15</t>
+          <t>-5,5; 15,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 9,46</t>
+          <t>-12,37; 9,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,83; -9,92</t>
+          <t>-30,48; -10,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 14,15</t>
+          <t>-1,21; 14,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 7,68</t>
+          <t>-7,44; 8,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,23; -6,24</t>
+          <t>-21,69; -6,9</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 82,65</t>
+          <t>-11,7; 79,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 55,26</t>
+          <t>-25,08; 54,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 22,3</t>
+          <t>-54,53; 20,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 54,73</t>
+          <t>-13,39; 53,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 32,23</t>
+          <t>-30,57; 33,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,75; -34,9</t>
+          <t>-77,67; -31,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 50,91</t>
+          <t>-3,47; 54,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 27,16</t>
+          <t>-20,56; 29,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -21,37</t>
+          <t>-61,29; -23,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 15,59</t>
+          <t>-1,32; 15,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 14,86</t>
+          <t>-1,04; 14,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 3,84</t>
+          <t>-12,34; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 24,72</t>
+          <t>9,3; 24,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,26</t>
+          <t>6,22; 20,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 8,0</t>
+          <t>-7,5; 7,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 17,86</t>
+          <t>6,98; 17,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 15,86</t>
+          <t>5,41; 16,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,82</t>
+          <t>-7,45; 2,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 64,17</t>
+          <t>-5,44; 63,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 63,23</t>
+          <t>-3,09; 62,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 15,59</t>
+          <t>-39,63; 14,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,24; 134,75</t>
+          <t>36,46; 136,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,26; 109,62</t>
+          <t>25,05; 110,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 42,33</t>
+          <t>-29,24; 36,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 80,22</t>
+          <t>26,08; 80,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 71,9</t>
+          <t>20,0; 73,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 12,57</t>
+          <t>-27,89; 11,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 18,44</t>
+          <t>-3,72; 18,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 18,23</t>
+          <t>-3,4; 17,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,88; -2,05</t>
+          <t>-20,97; -1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 13,38</t>
+          <t>-8,58; 13,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 18,42</t>
+          <t>-0,85; 19,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -3,98</t>
+          <t>-22,16; -4,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 12,62</t>
+          <t>-2,8; 13,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 14,46</t>
+          <t>0,59; 15,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -5,66</t>
+          <t>-18,95; -5,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 79,2</t>
+          <t>-11,38; 79,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 84,17</t>
+          <t>-9,62; 77,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,14; -9,01</t>
+          <t>-58,75; -6,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 53,54</t>
+          <t>-23,07; 52,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 74,75</t>
+          <t>-2,4; 74,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,33; -13,74</t>
+          <t>-60,21; -16,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 47,96</t>
+          <t>-8,26; 49,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 56,83</t>
+          <t>0,91; 57,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,02; -21,21</t>
+          <t>-54,4; -21,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 25,84</t>
+          <t>6,81; 25,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 17,08</t>
+          <t>-2,39; 15,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 20,71</t>
+          <t>-16,08; 16,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 19,22</t>
+          <t>0,32; 19,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 20,77</t>
+          <t>2,66; 21,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -7,67</t>
+          <t>-21,62; -8,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,05; 20,36</t>
+          <t>6,33; 20,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 16,51</t>
+          <t>3,04; 15,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 2,29</t>
+          <t>-16,85; 2,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,63; 111,65</t>
+          <t>22,29; 109,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 72,2</t>
+          <t>-7,13; 68,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 98,34</t>
+          <t>-54,98; 69,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 76,23</t>
+          <t>1,32; 82,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 83,54</t>
+          <t>7,0; 85,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,29; -31,9</t>
+          <t>-65,65; -32,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,27; 80,06</t>
+          <t>20,25; 80,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,76; 65,32</t>
+          <t>9,97; 61,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 15,63</t>
+          <t>-55,43; 16,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,16</t>
+          <t>5,33; 14,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,98</t>
+          <t>2,16; 11,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,41</t>
+          <t>-12,01; 3,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,66</t>
+          <t>5,97; 15,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,0</t>
+          <t>4,84; 14,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -7,06</t>
+          <t>-14,63; -6,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,26</t>
+          <t>7,16; 13,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,5</t>
+          <t>5,08; 11,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -2,76</t>
+          <t>-12,06; -4,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,67; 59,94</t>
+          <t>17,53; 56,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,85; 46,3</t>
+          <t>6,97; 43,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 14,36</t>
+          <t>-41,05; 18,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,91; 57,26</t>
+          <t>19,69; 58,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,63; 55,17</t>
+          <t>15,97; 56,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -26,22</t>
+          <t>-48,83; -26,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,88; 49,8</t>
+          <t>24,1; 51,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,61; 43,42</t>
+          <t>17,33; 43,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -8,34</t>
+          <t>-41,32; -14,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 18,71</t>
+          <t>-3,18; 19,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 12,47</t>
+          <t>-8,42; 12,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 4,53</t>
+          <t>-18,53; 5,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 15,65</t>
+          <t>-4,97; 17,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 9,62</t>
+          <t>-11,56; 10,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -10,06</t>
+          <t>-31,78; -10,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 14,76</t>
+          <t>-1,08; 14,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 8,04</t>
+          <t>-7,07; 8,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -6,9</t>
+          <t>-22,91; -6,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 79,53</t>
+          <t>-9,39; 87,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 54,63</t>
+          <t>-24,2; 56,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 20,69</t>
+          <t>-52,57; 22,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 53,68</t>
+          <t>-12,11; 62,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 33,31</t>
+          <t>-28,5; 39,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,67; -31,27</t>
+          <t>-78,14; -34,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 54,45</t>
+          <t>-3,07; 54,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 29,57</t>
+          <t>-19,76; 30,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,29; -23,99</t>
+          <t>-62,81; -20,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 15,19</t>
+          <t>-1,62; 14,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 14,96</t>
+          <t>0,68; 15,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 3,19</t>
+          <t>-12,0; 2,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 24,72</t>
+          <t>9,33; 24,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,47</t>
+          <t>6,55; 20,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 7,21</t>
+          <t>-7,14; 7,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 17,86</t>
+          <t>6,57; 17,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,13</t>
+          <t>5,28; 15,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,74</t>
+          <t>-7,61; 3,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 63,73</t>
+          <t>-5,6; 62,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 62,35</t>
+          <t>2,23; 65,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 14,02</t>
+          <t>-39,66; 12,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,46; 136,25</t>
+          <t>37,12; 128,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,05; 110,53</t>
+          <t>25,5; 113,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 36,75</t>
+          <t>-27,38; 41,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,08; 80,59</t>
+          <t>23,8; 78,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 73,34</t>
+          <t>20,04; 74,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 11,84</t>
+          <t>-28,08; 15,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 18,67</t>
+          <t>-3,22; 19,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 17,59</t>
+          <t>-3,08; 17,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -1,77</t>
+          <t>-21,91; -3,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 13,52</t>
+          <t>-7,9; 14,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 19,21</t>
+          <t>-2,18; 18,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -4,68</t>
+          <t>-22,2; -4,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 13,0</t>
+          <t>-2,37; 13,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 15,06</t>
+          <t>0,9; 15,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -5,57</t>
+          <t>-18,5; -6,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 79,74</t>
+          <t>-9,58; 85,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 77,12</t>
+          <t>-8,84; 73,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,75; -6,12</t>
+          <t>-59,27; -12,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 52,64</t>
+          <t>-21,37; 53,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 74,48</t>
+          <t>-5,94; 72,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,21; -16,96</t>
+          <t>-58,56; -15,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 49,38</t>
+          <t>-7,21; 49,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 57,78</t>
+          <t>2,31; 57,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -21,33</t>
+          <t>-53,77; -23,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 25,73</t>
+          <t>6,44; 25,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 15,82</t>
+          <t>-1,38; 17,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 16,69</t>
+          <t>-16,07; 21,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 19,79</t>
+          <t>1,02; 19,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 21,51</t>
+          <t>1,69; 20,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,62; -8,18</t>
+          <t>-22,36; -8,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,41</t>
+          <t>7,01; 19,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 15,77</t>
+          <t>1,96; 16,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 2,85</t>
+          <t>-16,81; 3,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,29; 109,04</t>
+          <t>20,76; 112,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 68,1</t>
+          <t>-4,42; 72,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 69,6</t>
+          <t>-55,21; 96,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 82,73</t>
+          <t>3,01; 82,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,0; 85,57</t>
+          <t>5,98; 86,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,65; -32,03</t>
+          <t>-66,03; -34,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,25; 80,61</t>
+          <t>22,21; 77,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 61,85</t>
+          <t>7,12; 63,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 16,96</t>
+          <t>-56,29; 19,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,83</t>
+          <t>5,19; 15,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,33</t>
+          <t>1,97; 11,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 3,93</t>
+          <t>-12,15; 3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,08</t>
+          <t>5,91; 14,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,03</t>
+          <t>5,17; 14,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -6,85</t>
+          <t>-14,75; -6,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,57</t>
+          <t>6,82; 13,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,51</t>
+          <t>4,87; 11,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,0</t>
+          <t>-12,44; -3,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,53; 56,42</t>
+          <t>17,01; 59,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,97; 43,22</t>
+          <t>6,6; 44,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 18,05</t>
+          <t>-41,18; 14,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,69; 58,15</t>
+          <t>19,92; 57,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,97; 56,1</t>
+          <t>16,86; 55,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,83; -26,66</t>
+          <t>-49,41; -26,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,1; 51,63</t>
+          <t>23,0; 50,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,33; 43,63</t>
+          <t>16,82; 43,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -14,38</t>
+          <t>-42,03; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-18,25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,04</t>
+          <t>-6,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,39</t>
+          <t>-12,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 19,48</t>
+          <t>-5,69; 16,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 12,87</t>
+          <t>-13,89; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 5,06</t>
+          <t>-28,82; -6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 17,6</t>
+          <t>-3,81; 18,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 10,97</t>
+          <t>-8,89; 12,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,78; -10,59</t>
+          <t>-17,92; 5,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 14,99</t>
+          <t>-1,59; 14,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 8,44</t>
+          <t>-7,84; 7,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -6,28</t>
+          <t>-20,54; -3,57</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-3,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-52,62%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>28,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-24,35%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,84%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-60,67%</t>
+          <t>-20,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-44,77%</t>
+          <t>-38,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 87,5</t>
+          <t>-14,19; 54,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 56,15</t>
+          <t>-34,51; 32,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,57; 22,18</t>
+          <t>-72,03; -21,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 62,06</t>
+          <t>-11,17; 82,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 39,52</t>
+          <t>-26,28; 55,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,14; -34,39</t>
+          <t>-53,74; 26,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 54,64</t>
+          <t>-4,32; 50,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 30,97</t>
+          <t>-21,93; 27,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,81; -20,29</t>
+          <t>-58,03; -12,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,68</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,39</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-5,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 14,96</t>
+          <t>9,42; 24,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 15,34</t>
+          <t>6,22; 20,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 2,89</t>
+          <t>-6,74; 8,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,33; 24,27</t>
+          <t>-1,97; 15,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 20,81</t>
+          <t>-0,9; 14,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 7,55</t>
+          <t>-12,34; 2,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,64</t>
+          <t>6,67; 17,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,71</t>
+          <t>5,3; 15,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 3,41</t>
+          <t>-7,57; 2,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>24,65%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>27,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-17,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>-18,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,22%</t>
+          <t>-9,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 62,04</t>
+          <t>36,24; 134,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 65,51</t>
+          <t>24,26; 109,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 12,89</t>
+          <t>-26,33; 42,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 128,33</t>
+          <t>-6,68; 64,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,5; 113,0</t>
+          <t>-3,62; 63,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 41,44</t>
+          <t>-40,24; 11,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 78,95</t>
+          <t>23,68; 80,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,04; 74,4</t>
+          <t>20,14; 71,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 15,02</t>
+          <t>-28,1; 11,4</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,32</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-12,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,85</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-11,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,32</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,95</t>
+          <t>-10,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-12,15</t>
+          <t>-11,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 19,95</t>
+          <t>-8,95; 13,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 17,3</t>
+          <t>-1,54; 18,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,91; -3,01</t>
+          <t>-21,9; -3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 14,22</t>
+          <t>-3,56; 18,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 18,36</t>
+          <t>-2,1; 18,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,2; -4,12</t>
+          <t>-19,56; -1,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 13,24</t>
+          <t>-2,12; 12,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 15,3</t>
+          <t>-0,04; 14,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -6,37</t>
+          <t>-19,32; -5,46</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-41,01%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>27,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>26,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-38,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,37%</t>
+          <t>-37,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-40,06%</t>
+          <t>-39,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 85,17</t>
+          <t>-23,58; 53,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 73,23</t>
+          <t>-4,58; 74,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,27; -12,05</t>
+          <t>-58,82; -12,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 53,07</t>
+          <t>-10,85; 79,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 72,26</t>
+          <t>-5,79; 84,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -15,91</t>
+          <t>-57,76; -7,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 49,25</t>
+          <t>-6,19; 47,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 57,15</t>
+          <t>-0,08; 56,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -23,28</t>
+          <t>-54,66; -20,26</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,71</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-14,98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>16,62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,61</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,95</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,71</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,11</t>
+          <t>-12,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,55</t>
+          <t>-13,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 25,94</t>
+          <t>0,85; 19,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 17,58</t>
+          <t>1,92; 20,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 21,76</t>
+          <t>-22,25; -7,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 19,92</t>
+          <t>5,62; 25,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 20,61</t>
+          <t>-2,26; 17,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,36; -8,71</t>
+          <t>-19,2; -4,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 19,78</t>
+          <t>6,05; 20,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,18</t>
+          <t>2,64; 16,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 3,69</t>
+          <t>-18,7; -8,63</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-51,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>59,71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>27,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34,32%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>40,39%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,09%</t>
+          <t>-45,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,14%</t>
+          <t>-48,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,76; 112,84</t>
+          <t>1,45; 76,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 72,57</t>
+          <t>5,6; 83,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,21; 96,97</t>
+          <t>-65,7; -30,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 82,63</t>
+          <t>19,63; 111,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 86,35</t>
+          <t>-6,78; 72,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,03; -34,76</t>
+          <t>-59,45; -17,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,21; 77,43</t>
+          <t>19,27; 80,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 63,74</t>
+          <t>8,76; 65,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 19,42</t>
+          <t>-59,75; -33,2</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-10,57</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>9,93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>6,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,88</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-9,72</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,99</t>
+          <t>-10,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,21</t>
+          <t>5,53; 14,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,23</t>
+          <t>4,85; 14,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 3,72</t>
+          <t>-14,77; -6,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,63</t>
+          <t>4,77; 15,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,24</t>
+          <t>2,59; 11,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -6,74</t>
+          <t>-14,13; -5,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,54</t>
+          <t>6,89; 13,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,43</t>
+          <t>5,0; 11,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -3,56</t>
+          <t>-13,04; -7,14</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-37,83%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,75%</t>
+          <t>-34,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-32,08%</t>
+          <t>-36,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,01; 59,31</t>
+          <t>17,91; 57,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,6; 44,69</t>
+          <t>15,63; 55,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 14,99</t>
+          <t>-48,51; -25,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,92; 57,51</t>
+          <t>15,67; 59,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,86; 55,33</t>
+          <t>7,85; 46,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -26,73</t>
+          <t>-45,9; -20,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,0; 50,72</t>
+          <t>22,88; 49,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,82; 43,64</t>
+          <t>16,61; 43,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -12,02</t>
+          <t>-44,25; -27,12</t>
         </is>
       </c>
     </row>
